--- a/reports/weekly_conversion/2026-07-25/Mellanni_Weekly_CEO_Overview_2026-07-25.xlsx
+++ b/reports/weekly_conversion/2026-07-25/Mellanni_Weekly_CEO_Overview_2026-07-25.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Products'!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top ASINs'!$A$1:$O$996</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Promos'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Keywords'!$A$1:$M$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Keywords'!$A$1:$Q$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57139,10 +57139,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -57154,7 +57154,11 @@
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="31" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -57223,6 +57227,26 @@
           <t>total_sales_wow</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>total_clicks</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>brand_clicks</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>brand_ctr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>brand_purchase_per_click</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -57239,34 +57263,46 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>74470</v>
+        <v>74564</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2592</v>
+        <v>2564</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J2" s="2" t="n">
+        <v>51023.6</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1626.68</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>49740.48</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>2440.02</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45030.96</v>
-      </c>
       <c r="M2" s="4" t="n">
-        <v>0.1045840461762308</v>
+        <v>0.0257962930796002</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32013</v>
+      </c>
+      <c r="O2" t="n">
+        <v>365</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.008752158066372501</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1205479452054794</v>
       </c>
     </row>
     <row r="3">
@@ -57293,25 +57329,37 @@
         <v>-2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>65429</v>
+        <v>65934</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1793</v>
+        <v>1618</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2" t="n">
+        <v>41242.82</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>778.4299999999999</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>45703.57</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>1229.1</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>50598.24</v>
-      </c>
       <c r="M3" s="4" t="n">
-        <v>-0.09673597342516251</v>
+        <v>-0.0976017847183491</v>
+      </c>
+      <c r="N3" t="n">
+        <v>29272</v>
+      </c>
+      <c r="O3" t="n">
+        <v>156</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0063780203606034</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1217948717948717</v>
       </c>
     </row>
     <row r="4">
@@ -57338,25 +57386,37 @@
         <v>-1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>56097</v>
+        <v>55981</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2065</v>
+        <v>1969</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="n">
+        <v>35422.31</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>924.25</v>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>34051.85</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>1552.74</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>30016.26</v>
-      </c>
       <c r="M4" s="4" t="n">
-        <v>0.1344467965029619</v>
+        <v>0.0402462714947939</v>
+      </c>
+      <c r="N4" t="n">
+        <v>25532</v>
+      </c>
+      <c r="O4" t="n">
+        <v>220</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0077065891337093</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1136363636363636</v>
       </c>
     </row>
     <row r="5">
@@ -57383,25 +57443,37 @@
         <v>15</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>67724</v>
+        <v>69302</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1746</v>
+        <v>1631</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" s="2" t="n">
+        <v>31869.74</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>174.85</v>
+      </c>
+      <c r="L5" s="2" t="n">
         <v>27901.08</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>104.91</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>25157.94</v>
-      </c>
       <c r="M5" s="4" t="n">
-        <v>0.1090367494317898</v>
+        <v>0.1422403720572822</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30785</v>
+      </c>
+      <c r="O5" t="n">
+        <v>50</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.004069672798307</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -57428,25 +57500,37 @@
         <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>33175</v>
+        <v>33686</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J6" s="2" t="n">
+        <v>23618.88</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>480.61</v>
+      </c>
+      <c r="L6" s="2" t="n">
         <v>22408.79</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>332.73</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>21689.15</v>
-      </c>
       <c r="M6" s="4" t="n">
-        <v>0.0331797235023041</v>
+        <v>0.0540006845528027</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13582</v>
+      </c>
+      <c r="O6" t="n">
+        <v>88</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0064388673446989</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1477272727272727</v>
       </c>
     </row>
     <row r="7">
@@ -57473,25 +57557,37 @@
         <v>-2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>28903</v>
+        <v>28638</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J7" s="2" t="n">
+        <v>21590.03</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1515.89</v>
+      </c>
+      <c r="L7" s="2" t="n">
         <v>21997.87</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>1679.77</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>22393.14</v>
-      </c>
       <c r="M7" s="4" t="n">
-        <v>-0.0176513878803955</v>
+        <v>-0.0185399768250289</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12751</v>
+      </c>
+      <c r="O7" t="n">
+        <v>273</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0148055751396496</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1355311355311355</v>
       </c>
     </row>
     <row r="8">
@@ -57518,25 +57614,37 @@
         <v>-2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>39577</v>
+        <v>39272</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1193</v>
+        <v>1016</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J8" s="2" t="n">
+        <v>15534.64</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>215.82</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>16892.88</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>431.64</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>17147.76</v>
-      </c>
       <c r="M8" s="4" t="n">
-        <v>-0.014863748967795</v>
+        <v>-0.0804031047399852</v>
+      </c>
+      <c r="N8" t="n">
+        <v>16534</v>
+      </c>
+      <c r="O8" t="n">
+        <v>93</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0071302614429195</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.06451612903225799</v>
       </c>
     </row>
     <row r="9">
@@ -57563,70 +57671,94 @@
         <v>2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>34013</v>
+        <v>32646</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1187</v>
+        <v>1322</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="n">
+        <v>14436.24</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>15407.26</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>139.88</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>12881.7</v>
-      </c>
       <c r="M9" s="4" t="n">
-        <v>0.1960579737146495</v>
+        <v>-0.0630235356578652</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14400</v>
+      </c>
+      <c r="O9" t="n">
+        <v>22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0040710584752035</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0909090909090909</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>twin sheets set</t>
+          <t>queen duvet cover</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B00O35CWQ8</t>
+          <t>B079YXK5SN</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>26991</v>
+        <v>27660</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1064</v>
+        <v>555</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14885.36</v>
+        <v>13869.45</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>69.94</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>14050.44</v>
+        <v>12969.32</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0594230500966517</v>
+        <v>0.0694045640018134</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13785</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0013428827215756</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -57653,346 +57785,442 @@
         <v>-2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28276</v>
+        <v>29364</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>669</v>
+        <v>648</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J11" s="2" t="n">
+        <v>13763.52</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>628.49</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>14209.56</v>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>1183.04</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>18792.48</v>
-      </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2438698883808842</v>
+        <v>-0.031390134529148</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11611</v>
+      </c>
+      <c r="O11" t="n">
+        <v>231</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0100882173115555</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0735930735930736</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>queen duvet cover</t>
+          <t>california king sheet sets</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B079YXK5SN</t>
+          <t>B00O35DNS4</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>27424</v>
+        <v>17142</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12969.32</v>
+        <v>13358.86</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>44.97</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>12955.2</v>
+        <v>12891.04</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0010899098431518</v>
+        <v>0.0362903225806451</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7876</v>
+      </c>
+      <c r="O12" t="n">
+        <v>33</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0092931568572233</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0303030303030303</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>california king sheet sets</t>
+          <t>twin sheets set</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B00O35DNS4</t>
+          <t>B00O35CWQ8</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>17959</v>
+        <v>25872</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>496</v>
+        <v>1177</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12891.04</v>
+        <v>12746.91</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>40.97</v>
+        <v>104.91</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>14709.55</v>
+        <v>14885.36</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1236278472149046</v>
+        <v>-0.1436612886755846</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11916</v>
+      </c>
+      <c r="O13" t="n">
+        <v>23</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0034425984134111</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pillow cases standard size</t>
+          <t>bed sheets queen size</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B00RKHWJ1O, B0822YG3V8</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>19613</v>
+        <v>22537</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1068</v>
+        <v>551</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12162.74</v>
+        <v>11703.24</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>110.91</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>9781.120000000001</v>
+        <v>11682</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2434915428907935</v>
+        <v>0.0018181818181817</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8539</v>
+      </c>
+      <c r="O14" t="n">
+        <v>49</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.005789224952741</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0612244897959183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bed sheets queen size</t>
+          <t>sheets</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00NLLUMOE, B0BTZ5HGMB</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>22926</v>
+        <v>59978</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>11682</v>
+        <v>11214.72</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>258.79</v>
+        <v>665.46</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>12669.93</v>
+        <v>11399.7</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.0779743850202801</v>
+        <v>-0.0162267428090212</v>
+      </c>
+      <c r="N15" t="n">
+        <v>18800</v>
+      </c>
+      <c r="O15" t="n">
+        <v>499</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.009040673974091799</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.0360721442885771</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>twin bed sheets</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B00NLLUMOE, B0BTZ5HGMB</t>
+          <t>B00O35CWQ8</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>58970</v>
+        <v>30048</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>481</v>
+        <v>943</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11399.7</v>
+        <v>10938.8</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>924.25</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>13394.64</v>
+        <v>10545.84</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.1489356936804573</v>
+        <v>0.0372620862823633</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11344</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0025591810620601</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bed sheets</t>
+          <t>pillow cases standard size</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00RKHWJ1O, B0822YG3V8</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>64171</v>
+        <v>19687</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>517</v>
+        <v>1150</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10981.08</v>
+        <v>10913.5</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>184.85</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>12230.68</v>
+        <v>12162.74</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.102169298845199</v>
+        <v>-0.1027104090032344</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8788</v>
+      </c>
+      <c r="O17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0152439024390243</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>twin bed sheets</t>
+          <t>queen size sheets</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B00O35CWQ8</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>30663</v>
+        <v>16054</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>776</v>
+        <v>593</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10545.84</v>
+        <v>10668.07</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>184.85</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9476.18</v>
+        <v>9735.27</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.11287881825799</v>
+        <v>0.09581655156970489</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6955</v>
+      </c>
+      <c r="O18" t="n">
+        <v>29</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0059401884473576</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1724137931034483</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>queen size sheets</t>
+          <t>bed sheets</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -58004,355 +58232,451 @@
         <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>16612</v>
+        <v>64570</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>573</v>
+        <v>478</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9735.27</v>
+        <v>10152.72</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>108.69</v>
+        <v>258.79</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9372.959999999999</v>
+        <v>10981.08</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.0386548112869357</v>
+        <v>-0.07543520309477759</v>
+      </c>
+      <c r="N19" t="n">
+        <v>19639</v>
+      </c>
+      <c r="O19" t="n">
+        <v>157</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0049378833149866</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0445859872611464</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>king size sheets</t>
+          <t>king sheet set</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B00NQDGAP2, B0BTZ24S9W</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14072</v>
+        <v>13291</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9671.129999999999</v>
+        <v>9775.530000000001</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>163.88</v>
+        <v>286.79</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7874.49</v>
+        <v>9379.92</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2281595379510291</v>
+        <v>0.042176265895658</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6199</v>
+      </c>
+      <c r="O20" t="n">
+        <v>62</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0094584286803966</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1129032258064516</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>king sheet set</t>
+          <t>king size sheets</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B00NQDGAP2, B0BTZ24S9W</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>13141</v>
+        <v>14101</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9379.92</v>
+        <v>9571.17</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>327.76</v>
+        <v>286.79</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9356.1</v>
+        <v>9671.129999999999</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.002545932600122</v>
+        <v>-0.0103359173126614</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5998</v>
+      </c>
+      <c r="O21" t="n">
+        <v>47</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.007078313253012</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1489361702127659</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cooling sheets</t>
+          <t>cooling sheets queen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B00NLLUMOE, B0BTZ5HGMB</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>39985</v>
+        <v>18433</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9145.290000000001</v>
+        <v>9404.639999999999</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>7122.5</v>
+        <v>9071.370000000001</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.2839999999999998</v>
+        <v>0.0367386624071116</v>
+      </c>
+      <c r="N22" t="n">
+        <v>9966</v>
+      </c>
+      <c r="O22" t="n">
+        <v>14</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0135004821600771</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cooling sheets queen</t>
+          <t>cooling sheets</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B00NLLUMOE, B0BTZ5HGMB</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-1</v>
-      </c>
       <c r="G23" s="3" t="n">
-        <v>19680</v>
+        <v>36897</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>363</v>
+        <v>266</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9071.370000000001</v>
+        <v>9041.34</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>10256.58</v>
+        <v>9145.290000000001</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1155560625471649</v>
+        <v>-0.0113665066936093</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17143</v>
+      </c>
+      <c r="O23" t="n">
+        <v>41</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.009246729815065399</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>deep pocket queen sheets</t>
+          <t>king bed sheets</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0822X4TLW</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>13471</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>323</v>
+      </c>
+      <c r="I24" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>17842</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>348</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" s="2" t="n">
-        <v>8452.92</v>
+        <v>8233.269999999999</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>245.82</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>7796.879999999999</v>
+        <v>6907.79</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0841413488472313</v>
+        <v>0.191881918819188</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5719</v>
+      </c>
+      <c r="O24" t="n">
+        <v>55</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.008353584447144499</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.109090909090909</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>queen sheets deep pocket</t>
+          <t>deep pocket queen sheets</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B0822X4TLW</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10960</v>
+        <v>17200</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8000.379999999999</v>
+        <v>7746.94</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>221.82</v>
+        <v>46.97</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>7521.99</v>
+        <v>8452.92</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.0635988614714988</v>
+        <v>-0.0835190679670456</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8764</v>
+      </c>
+      <c r="O25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0137268359643102</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>xl twin sheets</t>
+          <t>full size bed sheets</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B016P42ARU</t>
+          <t>B00O35DAL4</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>11201</v>
+        <v>20399</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>381</v>
+        <v>464</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7444.74</v>
+        <v>6992.48</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>107.91</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>6206.06</v>
+        <v>6895.5</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1995920116789072</v>
+        <v>0.0140642447973316</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7447</v>
+      </c>
+      <c r="O26" t="n">
+        <v>33</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0058500265910299</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.0909090909090909</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>king bed sheets</t>
+          <t>cooling sheets king size</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -58364,175 +58688,220 @@
         <v>1</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>13571</v>
+        <v>11823</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>271</v>
+        <v>204</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6907.79</v>
+        <v>6729.96</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>163.88</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>8587.719999999999</v>
+        <v>6235.110000000001</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1956200248727251</v>
+        <v>0.07936507936507919</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6170</v>
+      </c>
+      <c r="O27" t="n">
+        <v>17</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0166994106090373</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>full size bed sheets</t>
+          <t>xl twin sheets</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B00O35DAL4</t>
+          <t>B016P42ARU</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>19637</v>
+        <v>10651</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>450</v>
+        <v>344</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6895.5</v>
+        <v>6721.759999999999</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>71.94</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>7493.860000000001</v>
+        <v>7444.74</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.0798467011660213</v>
+        <v>-0.09711286089238851</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4801</v>
+      </c>
+      <c r="O28" t="n">
+        <v>5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0047846889952153</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>queen fitted sheet only</t>
+          <t>king pillow cases set of 2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B01ES3L33W</t>
+          <t>B00RKHX3E6</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2</v>
+        <v>-16</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12532</v>
+        <v>7863</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>660</v>
+        <v>462</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6593.400000000001</v>
+        <v>6652.8</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>6643.35</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>-0.0075187969924811</v>
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3793</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0279329608938547</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cooling sheets king size</t>
+          <t>queen sheets deep pocket</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>12823</v>
+        <v>11186</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>189</v>
+        <v>307</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6235.110000000001</v>
+        <v>6520.679999999999</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>110.91</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>5668.11</v>
+        <v>8000.379999999999</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1000333444481495</v>
+        <v>-0.1849537146985518</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5413</v>
+      </c>
+      <c r="O30" t="n">
+        <v>57</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0136887608069164</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.0526315789473684</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sheets king size</t>
+          <t>king size bed sheets</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -58544,34 +58913,46 @@
         <v>1</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>10682</v>
+        <v>8943</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="I31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>6168.58</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>122.91</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>4970.549999999999</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>0.2410256410256412</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3605</v>
+      </c>
+      <c r="O31" t="n">
         <v>9</v>
       </c>
-      <c r="J31" s="2" t="n">
-        <v>6177.94</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>368.73</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>6747.75</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>-0.0844444444444445</v>
+      <c r="P31" t="n">
+        <v>0.0036555645816409</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -58598,115 +58979,148 @@
         <v>-3</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>6862</v>
+        <v>6765</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J32" s="2" t="n">
+        <v>6138.36</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>554.55</v>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>6117.12</v>
       </c>
-      <c r="K32" s="2" t="n">
-        <v>221.82</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>5686.98</v>
-      </c>
       <c r="M32" s="4" t="n">
-        <v>0.0756359262736989</v>
+        <v>0.0034722222222221</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3134</v>
+      </c>
+      <c r="O32" t="n">
+        <v>53</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.0122685185185185</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.2830188679245283</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>deep pocket king sheet set</t>
+          <t>twin fitted sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0822X1VP7</t>
+          <t>B00O35CWQ8</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>46</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11048</v>
+        <v>12704</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>5997.599999999999</v>
+        <v>5724.27</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>5744.25</v>
+        <v>5504.49</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.044104974539757</v>
+        <v>0.0399274047186934</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5773</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>twin fitted sheet</t>
+          <t>sheets king size</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B00O35CWQ8</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>12887</v>
+        <v>10701</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>551</v>
+        <v>213</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5504.49</v>
+        <v>5429.37</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>204.85</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>6400.88</v>
+        <v>6177.94</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1400416817687568</v>
+        <v>-0.121168221122251</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4175</v>
+      </c>
+      <c r="O34" t="n">
+        <v>65</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.009148486980999199</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="35">
@@ -58724,40 +59138,52 @@
         <v>2</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>12785</v>
+        <v>13190</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="2" t="n">
+        <v>5260.95</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
         <v>5390.85</v>
       </c>
-      <c r="K35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>4923.839999999999</v>
-      </c>
       <c r="M35" s="4" t="n">
-        <v>0.09484670501072349</v>
+        <v>-0.0240963855421687</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5834</v>
+      </c>
+      <c r="O35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.003584229390681</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pillowcases</t>
+          <t>pillow case</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -58769,130 +59195,166 @@
         <v>2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>15437</v>
+        <v>13033</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5289.400000000001</v>
+        <v>5200.52</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>61.56</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4960.06</v>
+        <v>4890.2</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.0663983903420523</v>
+        <v>0.063457527299497</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4619</v>
+      </c>
+      <c r="O36" t="n">
+        <v>8</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.0068728522336769</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>king fitted sheet only</t>
+          <t>king sheets deep pocket</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B0822X1VP7</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>7025</v>
+        <v>7577</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>315</v>
+        <v>201</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>5036.849999999999</v>
+        <v>5123.49</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>4961.690000000001</v>
+        <v>4715.65</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.0151480644699686</v>
+        <v>0.08648648648648651</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3858</v>
+      </c>
+      <c r="O37" t="n">
+        <v>13</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0102120974076983</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>king size bed sheets</t>
+          <t>deep pocket king sheet set</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B0822X1VP7</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>8530</v>
+        <v>11161</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4970.549999999999</v>
+        <v>5007.03</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>40.97</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>6387.87</v>
+        <v>5997.599999999999</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-0.2218767758266841</v>
+        <v>-0.1651610644257702</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5984</v>
+      </c>
+      <c r="O38" t="n">
+        <v>6</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.0066371681415929</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pillow case</t>
+          <t>pillowcases</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -58904,169 +59366,217 @@
         <v>2</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>11</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>13067</v>
+        <v>15037</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4890.2</v>
+        <v>4801.940000000001</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>17.97</v>
+        <v>35.94</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>5001.23</v>
+        <v>5289.400000000001</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-0.0222005386674879</v>
+        <v>-0.0921579007070745</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5824</v>
+      </c>
+      <c r="O39" t="n">
+        <v>11</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.006979695431472</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>california king sheets</t>
+          <t>queen size sheet set</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>5415</v>
+        <v>7265</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4756.17</v>
+        <v>4796.61</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>40.97</v>
+        <v>36.97</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4336.9</v>
+        <v>4517.74</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.09667504438654349</v>
+        <v>0.0617277665381363</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3222</v>
+      </c>
+      <c r="O40" t="n">
+        <v>23</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.0100788781770376</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.0434782608695652</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>king sheets deep pocket</t>
+          <t>california king sheets</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0822X1VP7</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8118</v>
+        <v>5524</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4715.65</v>
+        <v>4652.21</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>5242.16</v>
+        <v>4756.17</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-0.1004376058723885</v>
+        <v>-0.0218579234972677</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2466</v>
+      </c>
+      <c r="O41" t="n">
+        <v>11</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.0055837563451776</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>queen size sheet set</t>
+          <t>king fitted sheet only</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>7056</v>
+        <v>6680</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>226</v>
+        <v>294</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4517.74</v>
+        <v>4407.06</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>110.91</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3746.6</v>
+        <v>5036.849999999999</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.2058239470453209</v>
+        <v>-0.1250364811340419</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3385</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.0049504950495049</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -59093,115 +59603,151 @@
         <v>0</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>9485</v>
+        <v>9632</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4502.88</v>
+        <v>4245.8</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>179.85</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4432.08</v>
+        <v>4502.88</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>0.0159744408945687</v>
+        <v>-0.0570923497850264</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4094</v>
+      </c>
+      <c r="O43" t="n">
+        <v>37</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.0073093638877913</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.1351351351351351</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bed sheets king size</t>
+          <t>sheets full size bed</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B00O35DAL4</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>8297</v>
+        <v>8868</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4501.42</v>
+        <v>4179.95</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>40.97</v>
+        <v>35.97</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4138.62</v>
+        <v>4261.51</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.0876620709318565</v>
+        <v>-0.0191387559808613</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3439</v>
+      </c>
+      <c r="O44" t="n">
+        <v>28</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.0052307117504203</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.0357142857142857</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sheets full size bed</t>
+          <t>pillow cases queen size set of 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B00O35DAL4</t>
+          <t>B014MVUDWM</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>8730</v>
+        <v>7618</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>209</v>
+        <v>411</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4261.51</v>
+        <v>4105.89</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>107.91</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>4701.759999999999</v>
+        <v>4125.87</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>-0.0936351493908662</v>
+        <v>-0.0048426150121064</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3483</v>
+      </c>
+      <c r="O45" t="n">
+        <v>9</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.01931330472103</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -59228,205 +59774,265 @@
         <v>2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10468</v>
+        <v>10608</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46" s="2" t="n">
+        <v>3914.88</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>107.91</v>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>4239.93</v>
       </c>
-      <c r="K46" s="2" t="n">
-        <v>35.97</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>3998</v>
-      </c>
       <c r="M46" s="4" t="n">
-        <v>0.0605127563781892</v>
+        <v>-0.0766640015283271</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3823</v>
+      </c>
+      <c r="O46" t="n">
+        <v>36</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.0071756029499701</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.0833333333333333</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pillow cases queen size set of 2</t>
+          <t>white sheets queen set</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B014MVUDWM</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>7902</v>
+        <v>2389</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>413</v>
+        <v>201</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4125.87</v>
+        <v>3615.99</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>554.55</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>4191.6</v>
+        <v>3335.14</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-0.015681362725451</v>
+        <v>0.0842093585276778</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1152</v>
+      </c>
+      <c r="O47" t="n">
+        <v>61</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.0211585154353104</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.2459016393442623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>queen fitted sheet</t>
+          <t>twin sheet set</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00O35CWQ8</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12</v>
+        <v>-13</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7470</v>
+        <v>6763</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>356</v>
+        <v>299</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3556.44</v>
+        <v>3468.4</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>3546.45</v>
+        <v>3547.87</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.0028169014084506</v>
+        <v>-0.0223993551060213</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3195</v>
+      </c>
+      <c r="O48" t="n">
+        <v>7</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.0036726128016789</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>twin sheet set</t>
+          <t>white pillow cases set of 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B00O35CWQ8</t>
+          <t>B00RKHX3E6</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-13</v>
+        <v>-6</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>7435</v>
+        <v>4427</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>263</v>
+        <v>494</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3547.87</v>
+        <v>3453.06</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>34.97</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>3090.84</v>
+        <v>3467.04</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>0.1478659522977571</v>
+        <v>-0.0040322580645161</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2057</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.0042372881355932</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>white pillow cases set of 2</t>
+          <t>bed sheets king size</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B00RKHX3E6</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>4347</v>
+        <v>8135</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>496</v>
+        <v>132</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3467.04</v>
+        <v>3364.68</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>81.94</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3693.52</v>
+        <v>4501.42</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>-0.0613182005241612</v>
+        <v>-0.2525292018962906</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3069</v>
+      </c>
+      <c r="O50" t="n">
+        <v>25</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.0073035349108968</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="51">
@@ -59453,31 +60059,43 @@
         <v>6</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>10112</v>
+        <v>10502</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="n">
+        <v>3259.1</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>3376.68</v>
       </c>
-      <c r="K51" s="2" t="n">
-        <v>71.94</v>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>3540</v>
-      </c>
       <c r="M51" s="4" t="n">
-        <v>-0.0461355932203389</v>
+        <v>-0.0348211853062772</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3905</v>
+      </c>
+      <c r="O51" t="n">
+        <v>17</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.0043125317097919</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>white sheets queen set</t>
+          <t>sheet &amp; pillowcase sets</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -59489,34 +60107,46 @@
         <v>1</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2177</v>
+        <v>17577</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>206</v>
+        <v>99</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3335.14</v>
+        <v>2876.94</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>406.67</v>
+        <v>215.82</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2800.87</v>
+        <v>2798.95</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.1907514450867051</v>
+        <v>0.0278640204362352</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4907</v>
+      </c>
+      <c r="O52" t="n">
+        <v>68</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.0060535920947209</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.088235294117647</v>
       </c>
     </row>
     <row r="53">
@@ -59543,343 +60173,433 @@
         <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>6655</v>
+        <v>6579</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="n">
+        <v>2863.61</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>35.97</v>
+      </c>
+      <c r="L53" s="2" t="n">
         <v>2902.8</v>
       </c>
-      <c r="K53" s="2" t="n">
-        <v>143.88</v>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>2945.28</v>
-      </c>
       <c r="M53" s="4" t="n">
-        <v>-0.0144230769230769</v>
+        <v>-0.0135007578889348</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2678</v>
+      </c>
+      <c r="O53" t="n">
+        <v>19</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.0044496487119437</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.0526315789473684</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sheet &amp; pillowcase sets</t>
+          <t>cal king sheet set</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00O35DNS4</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>20494</v>
+        <v>3901</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2798.95</v>
+        <v>2666.56</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>36.97</v>
+        <v>44.97</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3298.68</v>
+        <v>2780.93</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>-0.1514939309056957</v>
+        <v>-0.0411265296141937</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1796</v>
+      </c>
+      <c r="O54" t="n">
+        <v>8</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.0073732718894009</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cal king sheet set</t>
+          <t>white sheets</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B00O35DNS4</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>4536</v>
+        <v>6043</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2780.93</v>
+        <v>2604</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>3238.92</v>
+        <v>2728.18</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>-0.1414020722957034</v>
+        <v>-0.0455175245035151</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2455</v>
+      </c>
+      <c r="O55" t="n">
+        <v>28</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.0050152247895396</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>white sheets</t>
+          <t>king fitted sheet</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00NQDGAP2, B01ES3MMYG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>5808</v>
+        <v>4229</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="I56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>2593.29</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1990</v>
+      </c>
+      <c r="O56" t="n">
         <v>4</v>
       </c>
-      <c r="J56" s="2" t="n">
-        <v>2728.18</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>147.88</v>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>2728.18</v>
-      </c>
-      <c r="M56" s="4" t="n">
+      <c r="P56" t="n">
+        <v>0.0164609053497942</v>
+      </c>
+      <c r="Q56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>twin sheets set kids</t>
+          <t>white queen sheets</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B00O35CWQ8</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>4539</v>
+        <v>1109</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2429.44</v>
+        <v>2473.92</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>295.76</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>2266.6</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>0.09146739609988511</v>
+      </c>
+      <c r="N57" t="n">
+        <v>553</v>
+      </c>
+      <c r="O57" t="n">
+        <v>26</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.0193885160328113</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>white king sheets</t>
+          <t>fitted sheet king</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B01ES3MMYG</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>26</v>
+        <v>-20</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1002</v>
+        <v>4677</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2315.43</v>
+        <v>2394</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>491.64</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2236.27</v>
-      </c>
-      <c r="M58" s="4" t="n">
-        <v>0.0353982300884955</v>
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2344</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.0035714285714285</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>white queen sheets</t>
+          <t>king size fitted sheets only</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00NQDGAP2, B01ES3MMYG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>1030</v>
+        <v>3404</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2266.6</v>
+        <v>2183.95</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>110.91</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2719.92</v>
+        <v>2038.64</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>-0.1666666666666665</v>
+        <v>0.0712779107640386</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1720</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>king size fitted sheets only</t>
+          <t>cooling bed sheets</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B00NQDGAP2, B01ES3MMYG</t>
+          <t>B00O35DAL4</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>8682</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>2001.98</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>1656.85</v>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>0.2083049159549748</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4113</v>
+      </c>
+      <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="D60" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>3644</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>2038.64</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>2218.52</v>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v>-0.081081081081081</v>
+      <c r="P60" t="n">
+        <v>0.0023041474654377</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cal king sheets</t>
+          <t>white king sheets</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -59891,214 +60611,271 @@
         <v>1</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2671</v>
+        <v>922</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1949.25</v>
+        <v>1859.07</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>286.79</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1949.35</v>
+        <v>2315.43</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>-5.129915099912096e-05</v>
+        <v>-0.1970951399955947</v>
+      </c>
+      <c r="N61" t="n">
+        <v>439</v>
+      </c>
+      <c r="O61" t="n">
+        <v>40</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.0269541778975741</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.175</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fitted sheet</t>
+          <t>twin xl sheet sets</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B016P42ARU</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>10112</v>
+        <v>4138</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1858.76</v>
+        <v>1856.3</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1649.73</v>
+        <v>1797.68</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.1267055821255599</v>
+        <v>0.0326086956521739</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1839</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>twin xl sheet sets</t>
+          <t>cal king sheets</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B016P42ARU</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>2484</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1820.44</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>1949.25</v>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>-0.06608182634346529</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1209</v>
+      </c>
+      <c r="O63" t="n">
         <v>5</v>
       </c>
-      <c r="G63" s="3" t="n">
-        <v>4218</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>1797.68</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>1711.9</v>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>0.0501080670599918</v>
+      <c r="P63" t="n">
+        <v>0.0072886297376093</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cooling bed sheets</t>
+          <t>extra deep pocket queen sheets</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B00O35DAL4</t>
+          <t>B0822X4TLW</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>-35</v>
+        <v>-3</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>9734</v>
+        <v>3891</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1656.85</v>
+        <v>1733.02</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1889.37</v>
+        <v>1496.88</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>-0.1230674775189613</v>
+        <v>0.1577547966436856</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2068</v>
+      </c>
+      <c r="O64" t="n">
+        <v>9</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.009933774834437</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>queen sheet set deep pocket</t>
+          <t>fitted sheet</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="E65" s="3" t="n">
-        <v>28</v>
-      </c>
       <c r="F65" s="3" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2636</v>
+        <v>10390</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1635.48</v>
+        <v>1520.96</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1699.32</v>
+        <v>1858.76</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>-0.0375679683638162</v>
+        <v>-0.1817340592653166</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4014</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.0028653295128939</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -60125,790 +60902,1000 @@
         <v>3</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>11485</v>
+        <v>12084</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="n">
+        <v>1516.56</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="L66" s="2" t="n">
         <v>1614.15</v>
       </c>
-      <c r="K66" s="2" t="n">
-        <v>73.94</v>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>1820.61</v>
-      </c>
       <c r="M66" s="4" t="n">
-        <v>-0.1134015522270009</v>
+        <v>-0.0604590651426446</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4540</v>
+      </c>
+      <c r="O66" t="n">
+        <v>30</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.0041823504809703</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.0333333333333333</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>split king sheets</t>
+          <t>queen sheet set deep pocket</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B01N10ETBD, B0BTZ68TRH</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>2789</v>
+        <v>2593</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1559.74</v>
+        <v>1338.12</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>44.97</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1363.52</v>
+        <v>1635.48</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>0.1439069467261206</v>
+        <v>-0.1818181818181817</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1250</v>
+      </c>
+      <c r="O67" t="n">
+        <v>8</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.0098643649815043</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>extra deep pocket queen sheets</t>
+          <t>split king sheets</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0822X4TLW</t>
+          <t>B01N10ETBD, B0BTZ68TRH</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>2655</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D68" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>3879</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J68" s="2" t="n">
-        <v>1496.88</v>
+        <v>1147.2</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>46.97</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1769.04</v>
+        <v>1559.74</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>-0.1538461538461538</v>
+        <v>-0.2644928000820649</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1161</v>
+      </c>
+      <c r="O68" t="n">
+        <v>12</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.0073982737361282</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.0833333333333333</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>white sheets full</t>
+          <t>twin bed sheets kids</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B00O35DAL4</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-1</v>
+        <v>57</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1055</v>
+        <v>2680</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1165.59</v>
+        <v>1096.78</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>143.88</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>980</v>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v>0.1893775510204083</v>
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1085</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.002906976744186</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>flat sheets only</t>
+          <t>rv queen sheets</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B01ETTFKIE</t>
+          <t>B08V8V7VZF, B08V93R9LN</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>4968</v>
+        <v>1158</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>987.71</v>
+        <v>1043.86</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>69.94</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1088.91</v>
+        <v>687.4200000000001</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>-0.0929369736709187</v>
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="N70" t="n">
+        <v>627</v>
+      </c>
+      <c r="O70" t="n">
+        <v>11</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.0098302055406613</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>twin flat sheet</t>
+          <t>white sheets full</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B00NLLUMOE, B01ETTEBIO</t>
+          <t>B00O35DAL4</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>3046</v>
+        <v>1030</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>969.03</v>
+        <v>994</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>179.85</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>879.6199999999999</v>
+        <v>1165.59</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>0.1016461653896001</v>
+        <v>-0.1472129994251839</v>
+      </c>
+      <c r="N71" t="n">
+        <v>459</v>
+      </c>
+      <c r="O71" t="n">
+        <v>16</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.0126182965299684</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.3125</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>california king bed sheets</t>
+          <t>twin flat sheet</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B00O35DPN2</t>
+          <t>B00NLLUMOE, B01ETTEBIO</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>1231</v>
+        <v>3451</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>869.7099999999999</v>
+        <v>961.9299999999999</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>44.97</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>599.8</v>
+        <v>969.03</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.4499999999999999</v>
+        <v>-0.0073269145434092</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1419</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.0037105751391465</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>king flat sheet</t>
+          <t>king split sheets for adjustable bed</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B00NQDGAP2, B01ETTFKIE</t>
+          <t>B07BKMKJKQ, B0BTZ68TRH</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1954</v>
+        <v>838</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>805.38</v>
+        <v>916.1900000000001</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>19.97</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>714.45</v>
+        <v>679.83</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>0.1272727272727272</v>
+        <v>0.3476751540826383</v>
+      </c>
+      <c r="N73" t="n">
+        <v>381</v>
+      </c>
+      <c r="O73" t="n">
+        <v>5</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.0141242937853107</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>queen flat sheet only</t>
+          <t>king flat sheet</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B01ETTDTSM</t>
+          <t>B00NQDGAP2, B01ETTFKIE</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>1628</v>
+        <v>1553</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>779.22</v>
+        <v>883.4799999999999</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>839.16</v>
+        <v>805.38</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>-0.0714285714285713</v>
+        <v>0.0969728575330898</v>
+      </c>
+      <c r="N74" t="n">
+        <v>663</v>
+      </c>
+      <c r="O74" t="n">
+        <v>2</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.0030257186081694</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>white bed sheets</t>
+          <t>flat sheets only</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B01ETTFKIE</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2306</v>
+        <v>4975</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>777.0600000000001</v>
+        <v>797.3000000000001</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>36.97</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>672</v>
+        <v>987.71</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>0.1563392857142858</v>
+        <v>-0.1927792570693826</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.0074074074074074</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rv queen sheets</t>
+          <t>flat sheet</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B08V8V7VZF, B08V93R9LN</t>
+          <t>B00NQDGAP2, B01ETTFKIE</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1186</v>
+        <v>3946</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>687.4200000000001</v>
+        <v>789.21</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1349.46</v>
+        <v>539.46</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>-0.490596238495398</v>
+        <v>0.4629629629629629</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1375</v>
+      </c>
+      <c r="O76" t="n">
+        <v>2</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.0020304568527918</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>king split sheets for adjustable bed</t>
+          <t>queen flat sheet only</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B07BKMKJKQ, B0BTZ68TRH</t>
+          <t>B01ETTDTSM</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>790</v>
+        <v>1527</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>740.35</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>779.22</v>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>-0.0498832165498832</v>
+      </c>
+      <c r="N77" t="n">
+        <v>696</v>
+      </c>
+      <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="2" t="n">
-        <v>679.83</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>46.97</v>
-      </c>
-      <c r="L77" s="2" t="n">
+      <c r="P77" t="n">
+        <v>0.0034602076124567</v>
+      </c>
+      <c r="Q77" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>short queen sheets for rv</t>
+          <t>king size flat sheet only</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B08V8V7VZF</t>
+          <t>B00NQDGAP2, B01ETTFKIE</t>
         </is>
       </c>
       <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1921</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>738.92</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>879</v>
+      </c>
+      <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="D78" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>787</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>666.12</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>1030.71</v>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v>-0.3537270425240854</v>
+      <c r="P78" t="n">
+        <v>0.0032362459546925</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>flat sheet</t>
+          <t>white bed sheets</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B00NQDGAP2, B01ETTFKIE</t>
+          <t>B00NLLUMOE</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>15</v>
+        <v>-3</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>4125</v>
+        <v>2351</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>539.46</v>
+        <v>672</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>669.33</v>
+        <v>777.0600000000001</v>
       </c>
       <c r="M79" s="4" t="n">
-        <v>-0.1940298507462686</v>
+        <v>-0.1352019149100456</v>
+      </c>
+      <c r="N79" t="n">
+        <v>839</v>
+      </c>
+      <c r="O79" t="n">
+        <v>6</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.0027790643816581</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>grey queen sheet set</t>
+          <t>california king bed sheets</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B00SBZJ8NG, B0BTZ4CFWV</t>
+          <t>B00O35DPN2</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>351</v>
+        <v>1110</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>361.08</v>
+        <v>623.76</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>440.51</v>
+        <v>869.7099999999999</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>-0.1803137272706635</v>
+        <v>-0.2827954145634751</v>
+      </c>
+      <c r="N80" t="n">
+        <v>418</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>king size sheet sets</t>
+          <t>short queen sheets for rv</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B08V8V7VZF</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>890</v>
+        <v>681</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>239.92</v>
+        <v>611.76</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>599.8</v>
+        <v>666.12</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-0.0816069176724914</v>
+      </c>
+      <c r="N81" t="n">
+        <v>303</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.002710027100271</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>grey queen sheets</t>
+          <t>grey queen sheet set</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B00NLLUP4G</t>
+          <t>B00SBZJ8NG, B0BTZ4CFWV</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>240</v>
+        <v>342</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>216</v>
+        <v>477.6</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>39.97</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
+        <v>361.08</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>0.3226985709538052</v>
+      </c>
+      <c r="N82" t="n">
+        <v>154</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>rv sheets</t>
+          <t>king size sheet sets</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B08V8V7VZF</t>
+          <t>B00NQDGAP2</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>912</v>
+      </c>
+      <c r="H83" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="E83" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>639</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="I83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>153.12</v>
+        <v>404.39</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>199.92</v>
+        <v>239.92</v>
       </c>
       <c r="M83" s="4" t="n">
-        <v>-0.2340936374549819</v>
+        <v>0.6855201733911307</v>
+      </c>
+      <c r="N83" t="n">
+        <v>380</v>
+      </c>
+      <c r="O83" t="n">
+        <v>3</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.008064516129032201</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>light grey sheets</t>
+          <t>grey sheets</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -60920,139 +61907,175 @@
         <v>1</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0</v>
+        <v>1038</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0</v>
+        <v>367.77</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>439</v>
+      </c>
+      <c r="O84" t="n">
+        <v>3</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.0138888888888888</v>
+      </c>
+      <c r="Q84" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>gray king size sheets</t>
+          <t>grey bed sheets</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B00SU0QSZ8</t>
+          <t>B00SBZJ8NG, B0BTZ51FTP</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>164</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>king size flat sheet only</t>
+          <t>rv sheets</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B00NQDGAP2, B01ETTFKIE</t>
+          <t>B08V8V7VZF</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
+        <v>153.12</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>-0.34717868338558</v>
+      </c>
+      <c r="N86" t="n">
+        <v>231</v>
+      </c>
+      <c r="O86" t="n">
+        <v>7</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.0136452241715399</v>
+      </c>
+      <c r="Q86" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>gray sheets full</t>
+          <t>bedspreads &amp; coverlets</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B00SUF39K0</t>
+          <t>B01FWBWTGO</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2</v>
+        <v>-45</v>
       </c>
       <c r="G87" s="3" t="n">
         <v>0</v>
@@ -61070,31 +62093,37 @@
         <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>gray sheets</t>
+          <t>dark grey sheets</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B00SUF39K0, B0BTZ51FTP</t>
+          <t>B00NLLUP4G</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>0</v>
@@ -61112,31 +62141,37 @@
         <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>grey sheets full</t>
+          <t>fitted sheet full</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B00SUF39K0</t>
+          <t>B00O35DAL4</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0</v>
@@ -61154,31 +62189,37 @@
         <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>grey full size sheets</t>
+          <t>full size bed sheets kids</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B00SUF39K0</t>
+          <t>B00O35DAL4</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>-18</v>
+        <v>7</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0</v>
@@ -61196,31 +62237,37 @@
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>twin fitted sheets 2 pack</t>
+          <t>gray king size sheets</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B016P42ARU</t>
+          <t>B00SU0QSZ8</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-18</v>
+        <v>1</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
@@ -61238,31 +62285,37 @@
         <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kids twin sheets</t>
+          <t>gray queen sheet set</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B00NLLUMOE</t>
+          <t>B00SBZJ8NG, B0BTZ4CFWV</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>55</v>
+        <v>-3</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -61280,31 +62333,37 @@
         <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>dark grey sheets</t>
+          <t>gray sheets</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B00NLLUP4G</t>
+          <t>B00SUF39K0, B0BTZ51FTP</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
@@ -61322,31 +62381,37 @@
         <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>top split king sheets sets for adjustable bed</t>
+          <t>gray sheets full</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B00NQDGAP2</t>
+          <t>B00SUF39K0</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="G94" s="3" t="n">
         <v>0</v>
@@ -61364,31 +62429,37 @@
         <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>gray twin sheets</t>
+          <t>gray sheets queen</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B016P42E9E</t>
+          <t>B00SBZJ8NG, B0BTZ4CFWV</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>-36</v>
+        <v>-6</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
@@ -61406,31 +62477,37 @@
         <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>twin xl fitted sheet</t>
+          <t>gray twin sheets</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B01ES3MHXC</t>
+          <t>B016P42E9E</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>1</v>
+        <v>-36</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0</v>
@@ -61448,31 +62525,37 @@
         <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>fitted sheet king</t>
+          <t>grey full size sheets</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B01ES3MMYG</t>
+          <t>B00SUF39K0</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="G97" s="3" t="n">
         <v>0</v>
@@ -61490,10 +62573,13 @@
         <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>2086.07</v>
-      </c>
-      <c r="M97" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -61537,29 +62623,35 @@
       <c r="L98" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>grey sheets king</t>
+          <t>grey queen sheets</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B00NQDGCW8</t>
+          <t>B00NLLUP4G</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0</v>
@@ -61577,32 +62669,41 @@
         <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="M99" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>grey sheets queen size</t>
+          <t>grey sheets full</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B00NLLUP4G, B0BTZ4CFWV</t>
+          <t>B00SUF39K0</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="F100" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D100" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
       </c>
@@ -61619,18 +62720,24 @@
         <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>fitted sheet full</t>
+          <t>grey sheets king</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B00O35DAL4</t>
+          <t>B00NQDGCW8</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -61640,10 +62747,10 @@
         <v>48</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -61661,14 +62768,17 @@
         <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>1408.59</v>
-      </c>
-      <c r="M101" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M101"/>
+  <autoFilter ref="A1:Q101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/weekly_conversion/2026-07-25/Mellanni_Weekly_CEO_Overview_2026-07-25.xlsx
+++ b/reports/weekly_conversion/2026-07-25/Mellanni_Weekly_CEO_Overview_2026-07-25.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Products" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Top ASINs" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Promos" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Keywords" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="H10 Keywords" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SQP Diagnostics" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$10</definedName>
@@ -24,7 +25,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Products'!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Top ASINs'!$A$1:$O$996</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Promos'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Keywords'!$A$1:$Q$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'H10 Keywords'!$A$1:$U$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'SQP Diagnostics'!$A$1:$Q$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57139,6 +57141,2051 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:U30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>h10_asins</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>search_volume</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>organic_rank</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sponsored_rank</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cpr</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>iq_score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>title_density</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>competing_products</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>keyword_sales</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>trend</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>search_query_volume</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>total_purchases</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>brand_purchases</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>est_total_keyword_sales</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>est_brand_keyword_sales</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>brand_ctr</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>brand_purchase_per_click</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>opportunity_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>king size sheets set</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>130261</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>182.45319</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13026.1</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>2372</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L2" t="n">
+        <v>44</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-brand-header|section-sponsored-video; score=89.80</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>65934</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>1618</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>41242.82</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>778.4299999999999</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>0.0063780203606034</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>0.1217948717948717</v>
+      </c>
+      <c r="U2" t="n">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>twin sheets</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>74897</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F3" t="n">
+        <v>115.92751</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3744.85</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1792</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>17</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-video; score=84.20</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>32646</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>1322</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>14436.24</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0.0040710584752035</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="U3" t="n">
+        <v>71.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bed sheets</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>109567</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>159.11237</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2739.175</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1756</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored|section-sponsored-video; score=89.11</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>64570</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>478</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>10152.72</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>258.79</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0.0049378833149866</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0.0445859872611464</v>
+      </c>
+      <c r="U4" t="n">
+        <v>67.09999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>king sheets</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>69719</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>109.44443</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3485.95</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1612</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L5" t="n">
+        <v>72</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-video|section-sponsored-brand-header; score=85.29</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>28638</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>847</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>21590.03</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>1515.89</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0.0148055751396496</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0.1355311355311355</v>
+      </c>
+      <c r="U5" t="n">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sheets queen size bed set</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>59512</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>95.6918</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5951.2</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L6" t="n">
+        <v>42</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-video|section-sponsored-brand-header; score=89.63</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>29364</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>648</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>13763.52</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>628.49</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.0100882173115555</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0.0735930735930736</v>
+      </c>
+      <c r="U6" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>queen bed sheets</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>70938</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>109.28874</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3546.9</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>1367</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored|section-sponsored-video; score=89.67</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>33686</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>23618.88</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>480.61</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0.0064388673446989</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0.1477272727272727</v>
+      </c>
+      <c r="U7" t="n">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>queen size sheets</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>34418</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>65.50868</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1720.9</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>1357</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored|section-sponsored-video|section-sponsored-brand-header; score=83.21</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>16054</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>593</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>10668.07</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>184.85</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0.0059401884473576</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="U8" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cooling sheets</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>84671</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>131.09243</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2116.775</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>1356</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L9" t="n">
+        <v>44</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>match_type=organic; score=83.68</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>36897</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>9041.34</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0.009246729815065399</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>queen sheets</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>188972</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>252.31928</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9448.6</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1279</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>73</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-video; score=93.61</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>74564</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>2564</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>51023.6</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>1626.68</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0.008752158066372501</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0.1205479452054794</v>
+      </c>
+      <c r="U10" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>california king sheet sets</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>38359</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>71.80477</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9589.75</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>1262</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L11" t="n">
+        <v>43</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>match_type=organic|section-sponsored-brand-header; score=83.67</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>17142</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>514</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>13358.86</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>0.0092931568572233</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="U11" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>queen sheet set</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>112569</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>162.36349</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5628.45</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>1173</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored|section-sponsored-brand-header|section-sponsored-video; score=90.82</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>55981</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>1969</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>35422.31</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>924.25</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0.0077065891337093</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="U12" t="n">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bamboo sheets</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>130209</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>183.03383</v>
+      </c>
+      <c r="G13" t="n">
+        <v>32552.25</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>1115</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|section-sponsored-brand-header|section-sponsored-video; score=86.78</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>68.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cooling sheets queen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>50097</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" t="n">
+        <v>84.48795000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5009.7</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>1070</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L14" t="n">
+        <v>31</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>match_type=organic|section-sponsored-brand-header; score=81.30</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>18433</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>336</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>9404.639999999999</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>0.0135004821600771</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bed sheets queen size</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>45406</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F15" t="n">
+        <v>78.5844</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2270.3</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>1042</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L15" t="n">
+        <v>43</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|section-sponsored-brand-header|section-sponsored-video; score=81.06</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>22537</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>551</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>11703.24</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>110.91</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>0.005789224952741</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0.0612244897959183</v>
+      </c>
+      <c r="U15" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sheets</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>98465</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>153.28997</v>
+      </c>
+      <c r="G16" t="n">
+        <v>984.65</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>997</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>79</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored|section-sponsored-video; score=87.75</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>59978</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>528</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>11214.72</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>665.46</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0.009040673974091799</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0.0360721442885771</v>
+      </c>
+      <c r="U16" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>king sheet set</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>27090</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" t="n">
+        <v>59.35844</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2709</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>992</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L17" t="n">
+        <v>32</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-video|section-sponsored-brand-header; score=80.10</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>13291</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>423</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>9775.530000000001</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>286.79</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0.0094584286803966</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0.1129032258064516</v>
+      </c>
+      <c r="U17" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>full size sheets</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>84575</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>125.51677</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8457.5</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>981</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L18" t="n">
+        <v>29</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-video; score=87.19</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>39272</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>1016</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>15534.64</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>215.82</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>0.0071302614429195</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0.06451612903225799</v>
+      </c>
+      <c r="U18" t="n">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>twin xl sheets</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>156894</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" t="n">
+        <v>213.50394</v>
+      </c>
+      <c r="G19" t="n">
+        <v>26149</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>977</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>91</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|section-sponsored-video; score=87.75</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>69302</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>1631</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>31869.74</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>174.85</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>0.004069672798307</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>king size sheets</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>29177</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>62.80575</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1458.85</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>962</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L20" t="n">
+        <v>12</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored|section-sponsored-brand-header|section-sponsored-video; score=82.82</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>14101</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>383</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>9571.17</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>286.79</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>0.007078313253012</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0.1489361702127659</v>
+      </c>
+      <c r="U20" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>full sheet set</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>22007</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>52.02463</v>
+      </c>
+      <c r="G21" t="n">
+        <v>733.5666666666667</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>890</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>43</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-video|section-sponsored-brand-header; score=80.36</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>9632</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>4245.8</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>179.85</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>0.0073093638877913</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="U21" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>silk sheets</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>66098</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F22" t="n">
+        <v>103.52914</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13219.6</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>860</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L22" t="n">
+        <v>51</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>match_type=organic|section-sponsored-video; score=81.13</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>twin sheets set</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>65434</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" t="n">
+        <v>104.34528</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6543.400000000001</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>838</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L23" t="n">
+        <v>31</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|section-sponsored-video; score=83.80</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>25872</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>1177</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>12746.91</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>104.91</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>0.0034425984134111</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="U23" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>bamboo sheets queen size</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>32857</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F24" t="n">
+        <v>65.89991000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>32857</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>821</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L24" t="n">
+        <v>32</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>match_type=organic; score=80.44</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>queen bedding sets</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>50094</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F25" t="n">
+        <v>85.12690000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1669.8</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>732</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L25" t="n">
+        <v>58</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>match_type=organic|section-sponsored-brand-header|section-sponsored-video; score=79.96</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>queen sheets deep pocket</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>26068</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>55.25092000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2606.8</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>671</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L26" t="n">
+        <v>16</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored|section-sponsored-brand-header|section-sponsored-video; score=82.07</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>11186</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>6520.679999999999</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>110.91</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0.0136887608069164</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>0.0526315789473684</v>
+      </c>
+      <c r="U26" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>twin bed sheets</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>66786</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F27" t="n">
+        <v>104.0266</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6678.6</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>659</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L27" t="n">
+        <v>22</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|section-sponsored-video; score=81.23</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>30048</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>943</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>10938.8</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0.0025591810620601</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>full size bed sheets</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>38354</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>70.83504000000001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3835.4</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>567</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L28" t="n">
+        <v>15</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored|section-sponsored-video|section-sponsored-brand-header; score=81.94</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>20399</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>464</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>6992.48</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>107.91</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0.0058500265910299</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="U28" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bedding</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>69727</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>119.09175</v>
+      </c>
+      <c r="G29" t="n">
+        <v>697.27</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>328</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L29" t="n">
+        <v>69</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>match_type=ppc|organic|sponsored|section-sponsored-video; score=81.38</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bedsure king comforter set, beige soft prewashed bedding for all seasons, 3 pieces gentlesoft™ bed s</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B00NLLUMOE, B00NQDGAP2, B00O35DAL4, B016P42ARU, B0822X1VP7</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>29186</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>58.96134000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>116278.8844621514</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L30" t="n">
+        <v>128</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>match_type=organic|sponsored; score=83.44</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>39.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:U30"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -57298,10 +59345,10 @@
       <c r="O2" t="n">
         <v>365</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="4" t="n">
         <v>0.008752158066372501</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="4" t="n">
         <v>0.1205479452054794</v>
       </c>
     </row>
@@ -57355,10 +59402,10 @@
       <c r="O3" t="n">
         <v>156</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="4" t="n">
         <v>0.0063780203606034</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="4" t="n">
         <v>0.1217948717948717</v>
       </c>
     </row>
@@ -57412,10 +59459,10 @@
       <c r="O4" t="n">
         <v>220</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="4" t="n">
         <v>0.0077065891337093</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>0.1136363636363636</v>
       </c>
     </row>
@@ -57469,10 +59516,10 @@
       <c r="O5" t="n">
         <v>50</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="4" t="n">
         <v>0.004069672798307</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -57526,10 +59573,10 @@
       <c r="O6" t="n">
         <v>88</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="4" t="n">
         <v>0.0064388673446989</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="4" t="n">
         <v>0.1477272727272727</v>
       </c>
     </row>
@@ -57583,10 +59630,10 @@
       <c r="O7" t="n">
         <v>273</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="4" t="n">
         <v>0.0148055751396496</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="4" t="n">
         <v>0.1355311355311355</v>
       </c>
     </row>
@@ -57640,10 +59687,10 @@
       <c r="O8" t="n">
         <v>93</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="4" t="n">
         <v>0.0071302614429195</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="4" t="n">
         <v>0.06451612903225799</v>
       </c>
     </row>
@@ -57697,10 +59744,10 @@
       <c r="O9" t="n">
         <v>22</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="4" t="n">
         <v>0.0040710584752035</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="4" t="n">
         <v>0.0909090909090909</v>
       </c>
     </row>
@@ -57754,10 +59801,10 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="4" t="n">
         <v>0.0013428827215756</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -57811,10 +59858,10 @@
       <c r="O11" t="n">
         <v>231</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="4" t="n">
         <v>0.0100882173115555</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="4" t="n">
         <v>0.0735930735930736</v>
       </c>
     </row>
@@ -57868,10 +59915,10 @@
       <c r="O12" t="n">
         <v>33</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="4" t="n">
         <v>0.0092931568572233</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="4" t="n">
         <v>0.0303030303030303</v>
       </c>
     </row>
@@ -57925,10 +59972,10 @@
       <c r="O13" t="n">
         <v>23</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="4" t="n">
         <v>0.0034425984134111</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="4" t="n">
         <v>0.1304347826086956</v>
       </c>
     </row>
@@ -57982,10 +60029,10 @@
       <c r="O14" t="n">
         <v>49</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="4" t="n">
         <v>0.005789224952741</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="4" t="n">
         <v>0.0612244897959183</v>
       </c>
     </row>
@@ -58039,10 +60086,10 @@
       <c r="O15" t="n">
         <v>499</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="4" t="n">
         <v>0.009040673974091799</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="4" t="n">
         <v>0.0360721442885771</v>
       </c>
     </row>
@@ -58096,10 +60143,10 @@
       <c r="O16" t="n">
         <v>8</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="4" t="n">
         <v>0.0025591810620601</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -58153,10 +60200,10 @@
       <c r="O17" t="n">
         <v>10</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="4" t="n">
         <v>0.0152439024390243</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -58210,10 +60257,10 @@
       <c r="O18" t="n">
         <v>29</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="4" t="n">
         <v>0.0059401884473576</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" s="4" t="n">
         <v>0.1724137931034483</v>
       </c>
     </row>
@@ -58267,10 +60314,10 @@
       <c r="O19" t="n">
         <v>157</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" s="4" t="n">
         <v>0.0049378833149866</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" s="4" t="n">
         <v>0.0445859872611464</v>
       </c>
     </row>
@@ -58324,10 +60371,10 @@
       <c r="O20" t="n">
         <v>62</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="4" t="n">
         <v>0.0094584286803966</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="4" t="n">
         <v>0.1129032258064516</v>
       </c>
     </row>
@@ -58381,10 +60428,10 @@
       <c r="O21" t="n">
         <v>47</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="4" t="n">
         <v>0.007078313253012</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" s="4" t="n">
         <v>0.1489361702127659</v>
       </c>
     </row>
@@ -58438,10 +60485,10 @@
       <c r="O22" t="n">
         <v>14</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="4" t="n">
         <v>0.0135004821600771</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -58495,10 +60542,10 @@
       <c r="O23" t="n">
         <v>41</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="4" t="n">
         <v>0.009246729815065399</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -58552,10 +60599,10 @@
       <c r="O24" t="n">
         <v>55</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24" s="4" t="n">
         <v>0.008353584447144499</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24" s="4" t="n">
         <v>0.109090909090909</v>
       </c>
     </row>
@@ -58609,10 +60656,10 @@
       <c r="O25" t="n">
         <v>20</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25" s="4" t="n">
         <v>0.0137268359643102</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25" s="4" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -58666,10 +60713,10 @@
       <c r="O26" t="n">
         <v>33</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="4" t="n">
         <v>0.0058500265910299</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26" s="4" t="n">
         <v>0.0909090909090909</v>
       </c>
     </row>
@@ -58723,10 +60770,10 @@
       <c r="O27" t="n">
         <v>17</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27" s="4" t="n">
         <v>0.0166994106090373</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -58780,10 +60827,10 @@
       <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28" s="4" t="n">
         <v>0.0047846889952153</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -58834,10 +60881,10 @@
       <c r="O29" t="n">
         <v>5</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="4" t="n">
         <v>0.0279329608938547</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -58891,10 +60938,10 @@
       <c r="O30" t="n">
         <v>57</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30" s="4" t="n">
         <v>0.0136887608069164</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="4" t="n">
         <v>0.0526315789473684</v>
       </c>
     </row>
@@ -58948,10 +60995,10 @@
       <c r="O31" t="n">
         <v>9</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P31" s="4" t="n">
         <v>0.0036555645816409</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" s="4" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -59005,10 +61052,10 @@
       <c r="O32" t="n">
         <v>53</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32" s="4" t="n">
         <v>0.0122685185185185</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32" s="4" t="n">
         <v>0.2830188679245283</v>
       </c>
     </row>
@@ -59062,7 +61109,7 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P33" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -59116,10 +61163,10 @@
       <c r="O34" t="n">
         <v>65</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P34" s="4" t="n">
         <v>0.009148486980999199</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q34" s="4" t="n">
         <v>0.0769230769230769</v>
       </c>
     </row>
@@ -59173,10 +61220,10 @@
       <c r="O35" t="n">
         <v>6</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P35" s="4" t="n">
         <v>0.003584229390681</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -59230,10 +61277,10 @@
       <c r="O36" t="n">
         <v>8</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P36" s="4" t="n">
         <v>0.0068728522336769</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36" s="4" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -59287,10 +61334,10 @@
       <c r="O37" t="n">
         <v>13</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37" s="4" t="n">
         <v>0.0102120974076983</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -59344,10 +61391,10 @@
       <c r="O38" t="n">
         <v>6</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P38" s="4" t="n">
         <v>0.0066371681415929</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -59401,10 +61448,10 @@
       <c r="O39" t="n">
         <v>11</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39" s="4" t="n">
         <v>0.006979695431472</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39" s="4" t="n">
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -59458,10 +61505,10 @@
       <c r="O40" t="n">
         <v>23</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P40" s="4" t="n">
         <v>0.0100788781770376</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40" s="4" t="n">
         <v>0.0434782608695652</v>
       </c>
     </row>
@@ -59515,10 +61562,10 @@
       <c r="O41" t="n">
         <v>11</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P41" s="4" t="n">
         <v>0.0055837563451776</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -59572,10 +61619,10 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P42" s="4" t="n">
         <v>0.0049504950495049</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -59629,10 +61676,10 @@
       <c r="O43" t="n">
         <v>37</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P43" s="4" t="n">
         <v>0.0073093638877913</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43" s="4" t="n">
         <v>0.1351351351351351</v>
       </c>
     </row>
@@ -59686,10 +61733,10 @@
       <c r="O44" t="n">
         <v>28</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P44" s="4" t="n">
         <v>0.0052307117504203</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44" s="4" t="n">
         <v>0.0357142857142857</v>
       </c>
     </row>
@@ -59743,10 +61790,10 @@
       <c r="O45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P45" s="4" t="n">
         <v>0.01931330472103</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q45" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -59800,10 +61847,10 @@
       <c r="O46" t="n">
         <v>36</v>
       </c>
-      <c r="P46" t="n">
+      <c r="P46" s="4" t="n">
         <v>0.0071756029499701</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q46" s="4" t="n">
         <v>0.0833333333333333</v>
       </c>
     </row>
@@ -59857,10 +61904,10 @@
       <c r="O47" t="n">
         <v>61</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P47" s="4" t="n">
         <v>0.0211585154353104</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q47" s="4" t="n">
         <v>0.2459016393442623</v>
       </c>
     </row>
@@ -59914,10 +61961,10 @@
       <c r="O48" t="n">
         <v>7</v>
       </c>
-      <c r="P48" t="n">
+      <c r="P48" s="4" t="n">
         <v>0.0036726128016789</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q48" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -59971,10 +62018,10 @@
       <c r="O49" t="n">
         <v>2</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P49" s="4" t="n">
         <v>0.0042372881355932</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q49" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60028,10 +62075,10 @@
       <c r="O50" t="n">
         <v>25</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P50" s="4" t="n">
         <v>0.0073035349108968</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q50" s="4" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -60085,10 +62132,10 @@
       <c r="O51" t="n">
         <v>17</v>
       </c>
-      <c r="P51" t="n">
+      <c r="P51" s="4" t="n">
         <v>0.0043125317097919</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q51" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60142,10 +62189,10 @@
       <c r="O52" t="n">
         <v>68</v>
       </c>
-      <c r="P52" t="n">
+      <c r="P52" s="4" t="n">
         <v>0.0060535920947209</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q52" s="4" t="n">
         <v>0.088235294117647</v>
       </c>
     </row>
@@ -60199,10 +62246,10 @@
       <c r="O53" t="n">
         <v>19</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P53" s="4" t="n">
         <v>0.0044496487119437</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q53" s="4" t="n">
         <v>0.0526315789473684</v>
       </c>
     </row>
@@ -60256,10 +62303,10 @@
       <c r="O54" t="n">
         <v>8</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P54" s="4" t="n">
         <v>0.0073732718894009</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q54" s="4" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -60313,10 +62360,10 @@
       <c r="O55" t="n">
         <v>28</v>
       </c>
-      <c r="P55" t="n">
+      <c r="P55" s="4" t="n">
         <v>0.0050152247895396</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q55" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60367,10 +62414,10 @@
       <c r="O56" t="n">
         <v>4</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P56" s="4" t="n">
         <v>0.0164609053497942</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q56" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60424,10 +62471,10 @@
       <c r="O57" t="n">
         <v>26</v>
       </c>
-      <c r="P57" t="n">
+      <c r="P57" s="4" t="n">
         <v>0.0193885160328113</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Q57" s="4" t="n">
         <v>0.3076923076923077</v>
       </c>
     </row>
@@ -60478,10 +62525,10 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="P58" t="n">
+      <c r="P58" s="4" t="n">
         <v>0.0035714285714285</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q58" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60535,7 +62582,7 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="P59" t="n">
+      <c r="P59" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60589,10 +62636,10 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="P60" t="n">
+      <c r="P60" s="4" t="n">
         <v>0.0023041474654377</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="Q60" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60646,10 +62693,10 @@
       <c r="O61" t="n">
         <v>40</v>
       </c>
-      <c r="P61" t="n">
+      <c r="P61" s="4" t="n">
         <v>0.0269541778975741</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="Q61" s="4" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -60703,7 +62750,7 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="P62" t="n">
+      <c r="P62" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60757,10 +62804,10 @@
       <c r="O63" t="n">
         <v>5</v>
       </c>
-      <c r="P63" t="n">
+      <c r="P63" s="4" t="n">
         <v>0.0072886297376093</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="Q63" s="4" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -60814,10 +62861,10 @@
       <c r="O64" t="n">
         <v>9</v>
       </c>
-      <c r="P64" t="n">
+      <c r="P64" s="4" t="n">
         <v>0.009933774834437</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Q64" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60871,10 +62918,10 @@
       <c r="O65" t="n">
         <v>4</v>
       </c>
-      <c r="P65" t="n">
+      <c r="P65" s="4" t="n">
         <v>0.0028653295128939</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q65" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60928,10 +62975,10 @@
       <c r="O66" t="n">
         <v>30</v>
       </c>
-      <c r="P66" t="n">
+      <c r="P66" s="4" t="n">
         <v>0.0041823504809703</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Q66" s="4" t="n">
         <v>0.0333333333333333</v>
       </c>
     </row>
@@ -60985,10 +63032,10 @@
       <c r="O67" t="n">
         <v>8</v>
       </c>
-      <c r="P67" t="n">
+      <c r="P67" s="4" t="n">
         <v>0.0098643649815043</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="Q67" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61042,10 +63089,10 @@
       <c r="O68" t="n">
         <v>12</v>
       </c>
-      <c r="P68" t="n">
+      <c r="P68" s="4" t="n">
         <v>0.0073982737361282</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="Q68" s="4" t="n">
         <v>0.0833333333333333</v>
       </c>
     </row>
@@ -61096,10 +63143,10 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
-      <c r="P69" t="n">
+      <c r="P69" s="4" t="n">
         <v>0.002906976744186</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="Q69" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61153,10 +63200,10 @@
       <c r="O70" t="n">
         <v>11</v>
       </c>
-      <c r="P70" t="n">
+      <c r="P70" s="4" t="n">
         <v>0.0098302055406613</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="Q70" s="4" t="n">
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -61210,10 +63257,10 @@
       <c r="O71" t="n">
         <v>16</v>
       </c>
-      <c r="P71" t="n">
+      <c r="P71" s="4" t="n">
         <v>0.0126182965299684</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="Q71" s="4" t="n">
         <v>0.3125</v>
       </c>
     </row>
@@ -61267,10 +63314,10 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="P72" t="n">
+      <c r="P72" s="4" t="n">
         <v>0.0037105751391465</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="Q72" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61324,10 +63371,10 @@
       <c r="O73" t="n">
         <v>5</v>
       </c>
-      <c r="P73" t="n">
+      <c r="P73" s="4" t="n">
         <v>0.0141242937853107</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="Q73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61381,10 +63428,10 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="P74" t="n">
+      <c r="P74" s="4" t="n">
         <v>0.0030257186081694</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="Q74" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61438,10 +63485,10 @@
       <c r="O75" t="n">
         <v>4</v>
       </c>
-      <c r="P75" t="n">
+      <c r="P75" s="4" t="n">
         <v>0.0074074074074074</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="Q75" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61495,10 +63542,10 @@
       <c r="O76" t="n">
         <v>2</v>
       </c>
-      <c r="P76" t="n">
+      <c r="P76" s="4" t="n">
         <v>0.0020304568527918</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="Q76" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61552,10 +63599,10 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="P77" t="n">
+      <c r="P77" s="4" t="n">
         <v>0.0034602076124567</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="Q77" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61606,10 +63653,10 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="P78" t="n">
+      <c r="P78" s="4" t="n">
         <v>0.0032362459546925</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q78" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61663,10 +63710,10 @@
       <c r="O79" t="n">
         <v>6</v>
       </c>
-      <c r="P79" t="n">
+      <c r="P79" s="4" t="n">
         <v>0.0027790643816581</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="Q79" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61720,7 +63767,7 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="P80" t="n">
+      <c r="P80" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61774,10 +63821,10 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="P81" t="n">
+      <c r="P81" s="4" t="n">
         <v>0.002710027100271</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="Q81" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61831,7 +63878,7 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="P82" t="n">
+      <c r="P82" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61885,10 +63932,10 @@
       <c r="O83" t="n">
         <v>3</v>
       </c>
-      <c r="P83" t="n">
+      <c r="P83" s="4" t="n">
         <v>0.008064516129032201</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="Q83" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61939,10 +63986,10 @@
       <c r="O84" t="n">
         <v>3</v>
       </c>
-      <c r="P84" t="n">
+      <c r="P84" s="4" t="n">
         <v>0.0138888888888888</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="Q84" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -61993,7 +64040,7 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="P85" t="n">
+      <c r="P85" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -62047,10 +64094,10 @@
       <c r="O86" t="n">
         <v>7</v>
       </c>
-      <c r="P86" t="n">
+      <c r="P86" s="4" t="n">
         <v>0.0136452241715399</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="Q86" s="4" t="n">
         <v>0</v>
       </c>
     </row>
